--- a/docs/epexspot_prices.xlsx
+++ b/docs/epexspot_prices.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HU25"/>
+  <dimension ref="A1:HV25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1564,6 +1564,11 @@
           <t>27-janv</t>
         </is>
       </c>
+      <c r="HV1" t="inlineStr">
+        <is>
+          <t>01-mai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2453,6 +2458,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3342,6 +3352,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4231,6 +4246,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5120,6 +5140,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6009,6 +6034,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6898,6 +6928,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7787,6 +7822,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8676,6 +8716,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9565,6 +9610,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10454,6 +10504,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11343,6 +11398,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12232,6 +12292,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13121,6 +13186,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14010,6 +14080,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14899,6 +14974,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15788,6 +15868,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16677,6 +16762,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17566,6 +17656,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18455,6 +18550,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19344,6 +19444,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20233,6 +20338,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21122,6 +21232,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22011,6 +22126,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HV24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -22896,6 +23016,11 @@
         </is>
       </c>
       <c r="HU25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="HV25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -22912,7 +23037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B231"/>
+  <dimension ref="A1:B232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25215,6 +25340,16 @@
       </c>
       <c r="B231" t="n">
         <v>43.81</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>46.3</v>
       </c>
     </row>
   </sheetData>
@@ -25228,7 +25363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27407,6 +27542,16 @@
         <v>73.5</v>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/epexspot_prices.xlsx
+++ b/docs/epexspot_prices.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HV25"/>
+  <dimension ref="A1:HW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,6 +1569,11 @@
           <t>01-mai</t>
         </is>
       </c>
+      <c r="HW1" t="inlineStr">
+        <is>
+          <t>09-mai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2463,6 +2468,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3357,6 +3367,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4251,6 +4266,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5145,6 +5165,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6039,6 +6064,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6933,6 +6963,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7827,6 +7862,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8721,6 +8761,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9615,6 +9660,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10509,6 +10559,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11403,6 +11458,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12297,6 +12357,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13191,6 +13256,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14085,6 +14155,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14979,6 +15054,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15873,6 +15953,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16767,6 +16852,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17661,6 +17751,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18555,6 +18650,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19449,6 +19549,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20343,6 +20448,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21237,6 +21347,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22131,6 +22246,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HW24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23021,6 +23141,11 @@
         </is>
       </c>
       <c r="HV25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="HW25" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/epexspot_prices.xlsx
+++ b/docs/epexspot_prices.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HW25"/>
+  <dimension ref="A1:HX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1574,6 +1574,11 @@
           <t>09-mai</t>
         </is>
       </c>
+      <c r="HX1" t="inlineStr">
+        <is>
+          <t>12-mai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2473,6 +2478,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3372,6 +3382,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4271,6 +4286,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5170,6 +5190,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6069,6 +6094,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6968,6 +6998,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7867,6 +7902,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8766,6 +8806,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9665,6 +9710,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10564,6 +10614,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11463,6 +11518,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12362,6 +12422,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13261,6 +13326,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14160,6 +14230,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15059,6 +15134,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15958,6 +16038,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16857,6 +16942,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17756,6 +17846,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18655,6 +18750,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19554,6 +19654,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20453,6 +20558,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21352,6 +21462,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22251,6 +22366,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HX24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23146,6 +23266,11 @@
         </is>
       </c>
       <c r="HW25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="HX25" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/epexspot_prices.xlsx
+++ b/docs/epexspot_prices.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HX25"/>
+  <dimension ref="A1:HY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1579,6 +1579,11 @@
           <t>12-mai</t>
         </is>
       </c>
+      <c r="HY1" t="inlineStr">
+        <is>
+          <t>13-mai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2483,6 +2488,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3387,6 +3397,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4291,6 +4306,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5195,6 +5215,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6099,6 +6124,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7003,6 +7033,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7907,6 +7942,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8811,6 +8851,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9715,6 +9760,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10619,6 +10669,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11523,6 +11578,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12427,6 +12487,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13331,6 +13396,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14235,6 +14305,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15139,6 +15214,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16043,6 +16123,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16947,6 +17032,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17851,6 +17941,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18755,6 +18850,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19659,6 +19759,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20563,6 +20668,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21467,6 +21577,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22371,6 +22486,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HY24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23271,6 +23391,11 @@
         </is>
       </c>
       <c r="HX25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="HY25" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/epexspot_prices.xlsx
+++ b/docs/epexspot_prices.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HY25"/>
+  <dimension ref="A1:HZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,6 +1584,11 @@
           <t>13-mai</t>
         </is>
       </c>
+      <c r="HZ1" t="inlineStr">
+        <is>
+          <t>23-mai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2493,6 +2498,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3402,6 +3412,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4311,6 +4326,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5220,6 +5240,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6129,6 +6154,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7038,6 +7068,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7947,6 +7982,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8856,6 +8896,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9765,6 +9810,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10674,6 +10724,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11583,6 +11638,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12492,6 +12552,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13401,6 +13466,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14310,6 +14380,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15219,6 +15294,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16128,6 +16208,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17037,6 +17122,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17946,6 +18036,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18855,6 +18950,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19764,6 +19864,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20673,6 +20778,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21582,6 +21692,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22491,6 +22606,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="HZ24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23396,6 +23516,11 @@
         </is>
       </c>
       <c r="HY25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="HZ25" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/docs/epexspot_prices.xlsx
+++ b/docs/epexspot_prices.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HZ25"/>
+  <dimension ref="A1:IA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,11 @@
           <t>23-mai</t>
         </is>
       </c>
+      <c r="IA1" t="inlineStr">
+        <is>
+          <t>29-mai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2503,6 +2508,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3417,6 +3427,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4331,6 +4346,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5245,6 +5265,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6159,6 +6184,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7073,6 +7103,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7987,6 +8022,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8901,6 +8941,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9815,6 +9860,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10729,6 +10779,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11643,6 +11698,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12557,6 +12617,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13471,6 +13536,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14385,6 +14455,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15299,6 +15374,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16213,6 +16293,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17127,6 +17212,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18041,6 +18131,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18955,6 +19050,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19869,6 +19969,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20783,6 +20888,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21697,6 +21807,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -22611,6 +22726,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="IA24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23521,6 +23641,11 @@
         </is>
       </c>
       <c r="HZ25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="IA25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
